--- a/_build/interestelar_100_new.xlsx
+++ b/_build/interestelar_100_new.xlsx
@@ -11,6 +11,536 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="175">
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>GALAXIA</t>
+  </si>
+  <si>
+    <t>ACTIVO</t>
+  </si>
+  <si>
+    <t>FPIOS</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
+    <t>MARGEN</t>
+  </si>
+  <si>
+    <t>RES</t>
+  </si>
+  <si>
+    <t>SOLVE</t>
+  </si>
+  <si>
+    <t>ACTCOR</t>
+  </si>
+  <si>
+    <t>PASCOR</t>
+  </si>
+  <si>
+    <t>LIQUIDEZ</t>
+  </si>
+  <si>
+    <t>APALANCA</t>
+  </si>
+  <si>
+    <t>RENECO</t>
+  </si>
+  <si>
+    <t>RENFIN</t>
+  </si>
+  <si>
+    <t>EMPLEA</t>
+  </si>
+  <si>
+    <t>FLOTA</t>
+  </si>
+  <si>
+    <t>COSTOP</t>
+  </si>
+  <si>
+    <t>CAPEX</t>
+  </si>
+  <si>
+    <t>IMD</t>
+  </si>
+  <si>
+    <t>EFLO</t>
+  </si>
+  <si>
+    <t>RUTAS</t>
+  </si>
+  <si>
+    <t>IDIG</t>
+  </si>
+  <si>
+    <t>IDIVERSE</t>
+  </si>
+  <si>
+    <t>IFIDE</t>
+  </si>
+  <si>
+    <t>GMEDRUT</t>
+  </si>
+  <si>
+    <t>DIST</t>
+  </si>
+  <si>
+    <t>BMAL</t>
+  </si>
+  <si>
+    <t>RATIO</t>
+  </si>
+  <si>
+    <t>ACTIVOS_ACUM</t>
+  </si>
+  <si>
+    <t>DIM</t>
+  </si>
+  <si>
+    <t>sandworm freight</t>
+  </si>
+  <si>
+    <t>Kobol</t>
+  </si>
+  <si>
+    <t>Pequeña Nube de Magallanes</t>
+  </si>
+  <si>
+    <t>ANTIGUA</t>
+  </si>
+  <si>
+    <t>REDUCIDA</t>
+  </si>
+  <si>
+    <t>mon calamari freight co.</t>
+  </si>
+  <si>
+    <t>Romulus</t>
+  </si>
+  <si>
+    <t>Galaxia del Triángulo</t>
+  </si>
+  <si>
+    <t>darth vader logistics</t>
+  </si>
+  <si>
+    <t>Zegema Beach</t>
+  </si>
+  <si>
+    <t>sdf-1 freightworks</t>
+  </si>
+  <si>
+    <t>Mann</t>
+  </si>
+  <si>
+    <t>ripley interstellar freight</t>
+  </si>
+  <si>
+    <t>gungan haulage co.</t>
+  </si>
+  <si>
+    <t>LV-426</t>
+  </si>
+  <si>
+    <t>Vía Láctea</t>
+  </si>
+  <si>
+    <t>x-wing deliveries</t>
+  </si>
+  <si>
+    <t>Endor</t>
+  </si>
+  <si>
+    <t>Galaxia de Andrómeda</t>
+  </si>
+  <si>
+    <t>kelvin universe movers</t>
+  </si>
+  <si>
+    <t>quantum freightlines</t>
+  </si>
+  <si>
+    <t>atreides logistics</t>
+  </si>
+  <si>
+    <t>Vulcano</t>
+  </si>
+  <si>
+    <t>dagobah deliveries</t>
+  </si>
+  <si>
+    <t>Dagobah</t>
+  </si>
+  <si>
+    <t>xenomorph haulage</t>
+  </si>
+  <si>
+    <t>Hoth</t>
+  </si>
+  <si>
+    <t>solar flare logistics</t>
+  </si>
+  <si>
+    <t>Júpiter</t>
+  </si>
+  <si>
+    <t>crait cargo systems</t>
+  </si>
+  <si>
+    <t>Mül</t>
+  </si>
+  <si>
+    <t>Gran Nube de Magallanes</t>
+  </si>
+  <si>
+    <t>voyager haulage</t>
+  </si>
+  <si>
+    <t>Planet P</t>
+  </si>
+  <si>
+    <t>slave i cargo</t>
+  </si>
+  <si>
+    <t>babylon 5 logistics</t>
+  </si>
+  <si>
+    <t>discovery one haulage</t>
+  </si>
+  <si>
+    <t>zentraedi cargo lines</t>
+  </si>
+  <si>
+    <t>Miranda</t>
+  </si>
+  <si>
+    <t>lando's cargo</t>
+  </si>
+  <si>
+    <t>La Tierra (Final)</t>
+  </si>
+  <si>
+    <t>navoo freight co.</t>
+  </si>
+  <si>
+    <t>Mustafar</t>
+  </si>
+  <si>
+    <t>poe dameron cargo</t>
+  </si>
+  <si>
+    <t>tannhauser</t>
+  </si>
+  <si>
+    <t>gungan freight co.</t>
+  </si>
+  <si>
+    <t>Pandora</t>
+  </si>
+  <si>
+    <t>eva star transport</t>
+  </si>
+  <si>
+    <t>Risa</t>
+  </si>
+  <si>
+    <t>mandalorian logistics</t>
+  </si>
+  <si>
+    <t>skywalker freight co.</t>
+  </si>
+  <si>
+    <t>k-2so logistics</t>
+  </si>
+  <si>
+    <t>Naboo</t>
+  </si>
+  <si>
+    <t>razor star freight</t>
+  </si>
+  <si>
+    <t>Fhloston Paradise</t>
+  </si>
+  <si>
+    <t>alderaan freight</t>
+  </si>
+  <si>
+    <t>droid haulage systems</t>
+  </si>
+  <si>
+    <t>leeloo intergalactic transport</t>
+  </si>
+  <si>
+    <t>klendathu cargo systems</t>
+  </si>
+  <si>
+    <t>Klendathu</t>
+  </si>
+  <si>
+    <t>venator transport systems</t>
+  </si>
+  <si>
+    <t>Arrakis</t>
+  </si>
+  <si>
+    <t>orion intergalactic freight</t>
+  </si>
+  <si>
+    <t>Tierra</t>
+  </si>
+  <si>
+    <t>droideka freight lines</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>coruscant cargo</t>
+  </si>
+  <si>
+    <t>Coruscant</t>
+  </si>
+  <si>
+    <t>tusken freight lines</t>
+  </si>
+  <si>
+    <t>Caprica</t>
+  </si>
+  <si>
+    <t>betazoid transport</t>
+  </si>
+  <si>
+    <t>jedha star movers</t>
+  </si>
+  <si>
+    <t>photon pack freight</t>
+  </si>
+  <si>
+    <t>sy snootles haulage</t>
+  </si>
+  <si>
+    <t>tatooine movers</t>
+  </si>
+  <si>
+    <t>Tatooine</t>
+  </si>
+  <si>
+    <t>infinity freight co.</t>
+  </si>
+  <si>
+    <t>andor cargo lines</t>
+  </si>
+  <si>
+    <t>bene gesserit goods</t>
+  </si>
+  <si>
+    <t>borg freight lines</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>uhura cargo systems</t>
+  </si>
+  <si>
+    <t>janeway star transport</t>
+  </si>
+  <si>
+    <t>Qo'noS</t>
+  </si>
+  <si>
+    <t>geonosis freight</t>
+  </si>
+  <si>
+    <t>kobol cargo systems</t>
+  </si>
+  <si>
+    <t>eros star freight</t>
+  </si>
+  <si>
+    <t>MADURA</t>
+  </si>
+  <si>
+    <t>enterprise logistics</t>
+  </si>
+  <si>
+    <t>echo base transport</t>
+  </si>
+  <si>
+    <t>adama transport</t>
+  </si>
+  <si>
+    <t>raddus logistics</t>
+  </si>
+  <si>
+    <t>mustafar haulage</t>
+  </si>
+  <si>
+    <t>atlas star transport</t>
+  </si>
+  <si>
+    <t>hoth haulage</t>
+  </si>
+  <si>
+    <t>mos eisley haulage</t>
+  </si>
+  <si>
+    <t>tannhäuser freight</t>
+  </si>
+  <si>
+    <t>unn freightways</t>
+  </si>
+  <si>
+    <t>veritech haulage</t>
+  </si>
+  <si>
+    <t>bib fortuna haulage</t>
+  </si>
+  <si>
+    <t>event horizon haulage</t>
+  </si>
+  <si>
+    <t>naboo star movers</t>
+  </si>
+  <si>
+    <t>batty haulage</t>
+  </si>
+  <si>
+    <t>hyperion star haulage</t>
+  </si>
+  <si>
+    <t>rogue one freight</t>
+  </si>
+  <si>
+    <t>ALTA</t>
+  </si>
+  <si>
+    <t>mirror universe cargo</t>
+  </si>
+  <si>
+    <t>bajoran star transport</t>
+  </si>
+  <si>
+    <t>jovian logistics</t>
+  </si>
+  <si>
+    <t>star gate logistics</t>
+  </si>
+  <si>
+    <t>forest moon freight</t>
+  </si>
+  <si>
+    <t>solaris haulage</t>
+  </si>
+  <si>
+    <t>vulcan star freight</t>
+  </si>
+  <si>
+    <t>defiant cargo</t>
+  </si>
+  <si>
+    <t>rebel alliance transport</t>
+  </si>
+  <si>
+    <t>kashyyyk freight lines</t>
+  </si>
+  <si>
+    <t>shuttlepod movers</t>
+  </si>
+  <si>
+    <t>harkonnen heavy haul</t>
+  </si>
+  <si>
+    <t>RENOVADA</t>
+  </si>
+  <si>
+    <t>travis star haulage</t>
+  </si>
+  <si>
+    <t>seven of nine logistics</t>
+  </si>
+  <si>
+    <t>assimilator haulage</t>
+  </si>
+  <si>
+    <t>yoda logistics</t>
+  </si>
+  <si>
+    <t>super star logistics</t>
+  </si>
+  <si>
+    <t>andromeda cargo</t>
+  </si>
+  <si>
+    <t>io star transport</t>
+  </si>
+  <si>
+    <t>battle droid haulage</t>
+  </si>
+  <si>
+    <t>kamino movers</t>
+  </si>
+  <si>
+    <t>LV-223</t>
+  </si>
+  <si>
+    <t>dagobah freightlines</t>
+  </si>
+  <si>
+    <t>hal intergalactic freight</t>
+  </si>
+  <si>
+    <t>dune dynamics</t>
+  </si>
+  <si>
+    <t>sith transport corp.</t>
+  </si>
+  <si>
+    <t>kyber crystal shipping</t>
+  </si>
+  <si>
+    <t>zion cargo systems</t>
+  </si>
+  <si>
+    <t>moya cargo systems</t>
+  </si>
+  <si>
+    <t>Nueva Caprica</t>
+  </si>
+  <si>
+    <t>icarus star transport</t>
+  </si>
+  <si>
+    <t>ezra bridger haulage</t>
+  </si>
+  <si>
+    <t>home one cargo</t>
+  </si>
+  <si>
+    <t>chakotay cargo systems</t>
+  </si>
+  <si>
+    <t>hyperdrive express</t>
+  </si>
+  <si>
+    <t>arrakis freight</t>
+  </si>
+  <si>
+    <t>vega transport</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,178 +884,110 @@
   <dimension ref="A1:AE105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>NOMBRE</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>SEDE</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>GALAXIA</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ACTIVO</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FPIOS</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ING</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>MARGEN</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>RES</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SOLVE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ACTCOR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>PASCOR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LIQUIDEZ</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>APALANCA</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>RENECO</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>RENFIN</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>EMPLEA</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>FLOTA</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>COSTOP</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>IMD</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>EFLO</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>RUTAS</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>IDIG</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>IDIVERSE</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>IFIDE</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>GMEDRUT</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>DIST</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>BMAL</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>RATIO</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>ACTIVOS_ACUM</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>DIM</t>
-        </is>
+    <row r="1" spans="1:31" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sandworm freight</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="2" spans="1:31">
+      <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
       </c>
       <c r="D2">
         <v>17.55</v>
@@ -578,10 +1040,8 @@
       <c r="T2">
         <v>1.441948501862789</v>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U2" t="s">
+        <v>34</v>
       </c>
       <c r="V2">
         <v>70</v>
@@ -610,27 +1070,19 @@
       <c r="AD2">
         <v>17.55</v>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mon calamari freight co.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Romulus</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="3" spans="1:31">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
       </c>
       <c r="D3">
         <v>29.2</v>
@@ -683,10 +1135,8 @@
       <c r="T3">
         <v>0.5867131163804058</v>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U3" t="s">
+        <v>34</v>
       </c>
       <c r="V3">
         <v>332</v>
@@ -715,27 +1165,19 @@
       <c r="AD3">
         <v>46.75</v>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE3" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>darth vader logistics</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Zegema Beach</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="4" spans="1:31">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
       </c>
       <c r="D4">
         <v>29.37</v>
@@ -788,10 +1230,8 @@
       <c r="T4">
         <v>0.7890103516798435</v>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U4" t="s">
+        <v>34</v>
       </c>
       <c r="V4">
         <v>318</v>
@@ -820,27 +1260,19 @@
       <c r="AD4">
         <v>76.12</v>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sdf-1 freightworks</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mann</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="5" spans="1:31">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
       </c>
       <c r="D5">
         <v>36.95</v>
@@ -893,10 +1325,8 @@
       <c r="T5">
         <v>0.9078936478906664</v>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U5" t="s">
+        <v>34</v>
       </c>
       <c r="V5">
         <v>320</v>
@@ -925,27 +1355,19 @@
       <c r="AD5">
         <v>113.07</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ripley interstellar freight</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mann</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="6" spans="1:31">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
       </c>
       <c r="D6">
         <v>37.07</v>
@@ -998,10 +1420,8 @@
       <c r="T6">
         <v>1.101115335346641</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U6" t="s">
+        <v>34</v>
       </c>
       <c r="V6">
         <v>2915</v>
@@ -1030,27 +1450,19 @@
       <c r="AD6">
         <v>150.14</v>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE6" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>gungan haulage co.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LV-426</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="7" spans="1:31">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
       </c>
       <c r="D7">
         <v>40.06</v>
@@ -1103,10 +1515,8 @@
       <c r="T7">
         <v>1.891546219920469</v>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U7" t="s">
+        <v>34</v>
       </c>
       <c r="V7">
         <v>153</v>
@@ -1135,27 +1545,19 @@
       <c r="AD7">
         <v>190.2</v>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE7" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>x-wing deliveries</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Endor</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="8" spans="1:31">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
       </c>
       <c r="D8">
         <v>40.35</v>
@@ -1208,10 +1610,8 @@
       <c r="T8">
         <v>1.537739061960944</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U8" t="s">
+        <v>34</v>
       </c>
       <c r="V8">
         <v>64</v>
@@ -1240,27 +1640,19 @@
       <c r="AD8">
         <v>230.55</v>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE8" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>kelvin universe movers</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Romulus</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="9" spans="1:31">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
       </c>
       <c r="D9">
         <v>43.03</v>
@@ -1313,10 +1705,8 @@
       <c r="T9">
         <v>1.196517081823375</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U9" t="s">
+        <v>34</v>
       </c>
       <c r="V9">
         <v>352</v>
@@ -1345,27 +1735,19 @@
       <c r="AD9">
         <v>273.58</v>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE9" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>quantum freightlines</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mann</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="10" spans="1:31">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
       </c>
       <c r="D10">
         <v>43.26</v>
@@ -1418,10 +1800,8 @@
       <c r="T10">
         <v>1.392315632013198</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U10" t="s">
+        <v>34</v>
       </c>
       <c r="V10">
         <v>160</v>
@@ -1450,27 +1830,19 @@
       <c r="AD10">
         <v>316.84</v>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE10" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>atreides logistics</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Vulcano</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="11" spans="1:31">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
       </c>
       <c r="D11">
         <v>43.52</v>
@@ -1523,10 +1895,8 @@
       <c r="T11">
         <v>1.599712129083528</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U11" t="s">
+        <v>34</v>
       </c>
       <c r="V11">
         <v>321</v>
@@ -1555,27 +1925,19 @@
       <c r="AD11">
         <v>360.36</v>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE11" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dagobah deliveries</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dagobah</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="12" spans="1:31">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
       </c>
       <c r="D12">
         <v>43.53</v>
@@ -1628,10 +1990,8 @@
       <c r="T12">
         <v>1.094045189683052</v>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U12" t="s">
+        <v>34</v>
       </c>
       <c r="V12">
         <v>311</v>
@@ -1660,27 +2020,19 @@
       <c r="AD12">
         <v>403.89</v>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE12" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>xenomorph haulage</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Hoth</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="13" spans="1:31">
+      <c r="A13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
       </c>
       <c r="D13">
         <v>43.66</v>
@@ -1733,10 +2085,8 @@
       <c r="T13">
         <v>1.443591963527791</v>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U13" t="s">
+        <v>34</v>
       </c>
       <c r="V13">
         <v>89</v>
@@ -1765,27 +2115,19 @@
       <c r="AD13">
         <v>447.55</v>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE13" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>solar flare logistics</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Júpiter</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="14" spans="1:31">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
       </c>
       <c r="D14">
         <v>44.32</v>
@@ -1838,10 +2180,8 @@
       <c r="T14">
         <v>0.761337965585663</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U14" t="s">
+        <v>34</v>
       </c>
       <c r="V14">
         <v>176</v>
@@ -1870,27 +2210,19 @@
       <c r="AD14">
         <v>491.87</v>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE14" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>crait cargo systems</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Mül</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="15" spans="1:31">
+      <c r="A15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" t="s">
+        <v>62</v>
       </c>
       <c r="D15">
         <v>44.44</v>
@@ -1943,10 +2275,8 @@
       <c r="T15">
         <v>1.888710416424035</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U15" t="s">
+        <v>34</v>
       </c>
       <c r="V15">
         <v>408</v>
@@ -1975,27 +2305,19 @@
       <c r="AD15">
         <v>536.3100000000001</v>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE15" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>voyager haulage</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Planet P</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="16" spans="1:31">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
       </c>
       <c r="D16">
         <v>44.82</v>
@@ -2048,10 +2370,8 @@
       <c r="T16">
         <v>0.4779202472567501</v>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U16" t="s">
+        <v>34</v>
       </c>
       <c r="V16">
         <v>368</v>
@@ -2080,27 +2400,19 @@
       <c r="AD16">
         <v>581.13</v>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE16" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>slave i cargo</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Júpiter</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="17" spans="1:31">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
       </c>
       <c r="D17">
         <v>45.01</v>
@@ -2153,10 +2465,8 @@
       <c r="T17">
         <v>2.660328294362007</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U17" t="s">
+        <v>34</v>
       </c>
       <c r="V17">
         <v>410</v>
@@ -2185,27 +2495,19 @@
       <c r="AD17">
         <v>626.14</v>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE17" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>babylon 5 logistics</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Dagobah</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="18" spans="1:31">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>49</v>
       </c>
       <c r="D18">
         <v>46.26</v>
@@ -2255,10 +2557,8 @@
       <c r="T18">
         <v>0.9242113781871648</v>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U18" t="s">
+        <v>34</v>
       </c>
       <c r="V18">
         <v>327</v>
@@ -2287,27 +2587,19 @@
       <c r="AD18">
         <v>672.4</v>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE18" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>discovery one haulage</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Romulus</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="19" spans="1:31">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
       </c>
       <c r="D19">
         <v>46.98</v>
@@ -2360,10 +2652,8 @@
       <c r="T19">
         <v>2.303268212078594</v>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U19" t="s">
+        <v>34</v>
       </c>
       <c r="V19">
         <v>354</v>
@@ -2392,27 +2682,19 @@
       <c r="AD19">
         <v>719.38</v>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE19" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>zentraedi cargo lines</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Miranda</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="20" spans="1:31">
+      <c r="A20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
       </c>
       <c r="D20">
         <v>48.09</v>
@@ -2465,10 +2747,8 @@
       <c r="T20">
         <v>1.227523242571593</v>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U20" t="s">
+        <v>34</v>
       </c>
       <c r="V20">
         <v>176</v>
@@ -2497,27 +2777,19 @@
       <c r="AD20">
         <v>767.47</v>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE20" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>lando's cargo</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>La Tierra (Final)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="21" spans="1:31">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>38</v>
       </c>
       <c r="D21">
         <v>48.7</v>
@@ -2570,10 +2842,8 @@
       <c r="T21">
         <v>2.244851141595696</v>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U21" t="s">
+        <v>34</v>
       </c>
       <c r="V21">
         <v>386</v>
@@ -2602,27 +2872,19 @@
       <c r="AD21">
         <v>816.17</v>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE21" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>navoo freight co.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Mustafar</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="22" spans="1:31">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>49</v>
       </c>
       <c r="D22">
         <v>49.62</v>
@@ -2675,10 +2937,8 @@
       <c r="T22">
         <v>2.004407242664578</v>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U22" t="s">
+        <v>34</v>
       </c>
       <c r="V22">
         <v>162</v>
@@ -2707,27 +2967,19 @@
       <c r="AD22">
         <v>865.79</v>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE22" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>poe dameron cargo</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Vulcano</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="23" spans="1:31">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
       </c>
       <c r="D23">
         <v>49.68</v>
@@ -2777,10 +3029,8 @@
       <c r="T23">
         <v>1.087217466171057</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U23" t="s">
+        <v>34</v>
       </c>
       <c r="V23">
         <v>168</v>
@@ -2809,27 +3059,19 @@
       <c r="AD23">
         <v>915.47</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE23" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>tannhauser</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="24" spans="1:31">
+      <c r="A24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>33</v>
       </c>
       <c r="D24">
         <v>49.82</v>
@@ -2882,10 +3124,8 @@
       <c r="T24">
         <v>1.694791997403922</v>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U24" t="s">
+        <v>34</v>
       </c>
       <c r="V24">
         <v>313</v>
@@ -2914,27 +3154,19 @@
       <c r="AD24">
         <v>965.29</v>
       </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE24" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>gungan freight co.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Pandora</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="25" spans="1:31">
+      <c r="A25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>46</v>
       </c>
       <c r="D25">
         <v>50.44</v>
@@ -2987,10 +3219,8 @@
       <c r="T25">
         <v>1.661915782645113</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U25" t="s">
+        <v>34</v>
       </c>
       <c r="V25">
         <v>177</v>
@@ -3019,27 +3249,19 @@
       <c r="AD25">
         <v>1015.73</v>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE25" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>eva star transport</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Risa</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="26" spans="1:31">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>38</v>
       </c>
       <c r="D26">
         <v>50.64</v>
@@ -3092,10 +3314,8 @@
       <c r="T26">
         <v>1.017595223622726</v>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U26" t="s">
+        <v>34</v>
       </c>
       <c r="V26">
         <v>393</v>
@@ -3124,27 +3344,19 @@
       <c r="AD26">
         <v>1066.37</v>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE26" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>mandalorian logistics</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Mül</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="27" spans="1:31">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
       </c>
       <c r="D27">
         <v>51.06</v>
@@ -3197,10 +3409,8 @@
       <c r="T27">
         <v>1.429056125646147</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U27" t="s">
+        <v>34</v>
       </c>
       <c r="V27">
         <v>90</v>
@@ -3229,27 +3439,19 @@
       <c r="AD27">
         <v>1117.43</v>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE27" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>skywalker freight co.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>La Tierra (Final)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="28" spans="1:31">
+      <c r="A28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" t="s">
+        <v>38</v>
       </c>
       <c r="D28">
         <v>51.26</v>
@@ -3302,10 +3504,8 @@
       <c r="T28">
         <v>1.871278725977085</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U28" t="s">
+        <v>34</v>
       </c>
       <c r="V28">
         <v>386</v>
@@ -3334,27 +3534,19 @@
       <c r="AD28">
         <v>1168.69</v>
       </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE28" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>k-2so logistics</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Naboo</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="29" spans="1:31">
+      <c r="A29" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
       </c>
       <c r="D29">
         <v>51.35</v>
@@ -3407,10 +3599,8 @@
       <c r="T29">
         <v>0.5965016061679491</v>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U29" t="s">
+        <v>34</v>
       </c>
       <c r="V29">
         <v>328</v>
@@ -3439,27 +3629,19 @@
       <c r="AD29">
         <v>1220.04</v>
       </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE29" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>razor star freight</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Fhloston Paradise</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="30" spans="1:31">
+      <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
       </c>
       <c r="D30">
         <v>51.59</v>
@@ -3512,10 +3694,8 @@
       <c r="T30">
         <v>1.28160170877807</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U30" t="s">
+        <v>34</v>
       </c>
       <c r="V30">
         <v>163</v>
@@ -3544,27 +3724,19 @@
       <c r="AD30">
         <v>1271.63</v>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE30" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>alderaan freight</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Pandora</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="31" spans="1:31">
+      <c r="A31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
       </c>
       <c r="D31">
         <v>52</v>
@@ -3617,10 +3789,8 @@
       <c r="T31">
         <v>1.407580023821418</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U31" t="s">
+        <v>34</v>
       </c>
       <c r="V31">
         <v>385</v>
@@ -3646,27 +3816,19 @@
       <c r="AD31">
         <v>1323.63</v>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE31" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>droid haulage systems</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Planet P</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="32" spans="1:31">
+      <c r="A32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>46</v>
       </c>
       <c r="D32">
         <v>52.19</v>
@@ -3719,10 +3881,8 @@
       <c r="T32">
         <v>1.217306929743248</v>
       </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U32" t="s">
+        <v>34</v>
       </c>
       <c r="V32">
         <v>209</v>
@@ -3751,27 +3911,19 @@
       <c r="AD32">
         <v>1375.82</v>
       </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE32" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>leeloo intergalactic transport</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Endor</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="33" spans="1:31">
+      <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
       </c>
       <c r="D33">
         <v>52.46</v>
@@ -3824,10 +3976,8 @@
       <c r="T33">
         <v>0.757239185813638</v>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U33" t="s">
+        <v>34</v>
       </c>
       <c r="V33">
         <v>384</v>
@@ -3856,27 +4006,19 @@
       <c r="AD33">
         <v>1428.28</v>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE33" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>klendathu cargo systems</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Klendathu</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="34" spans="1:31">
+      <c r="A34" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
+        <v>46</v>
       </c>
       <c r="D34">
         <v>52.83</v>
@@ -3926,10 +4068,8 @@
       <c r="T34">
         <v>0.8599584802701462</v>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U34" t="s">
+        <v>34</v>
       </c>
       <c r="V34">
         <v>120</v>
@@ -3958,27 +4098,19 @@
       <c r="AD34">
         <v>1481.11</v>
       </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE34" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>venator transport systems</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Arrakis</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="35" spans="1:31">
+      <c r="A35" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" t="s">
+        <v>62</v>
       </c>
       <c r="D35">
         <v>53.42</v>
@@ -4031,10 +4163,8 @@
       <c r="T35">
         <v>2.393860704362713</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U35" t="s">
+        <v>34</v>
       </c>
       <c r="V35">
         <v>131</v>
@@ -4060,27 +4190,19 @@
       <c r="AD35">
         <v>1534.53</v>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE35" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>orion intergalactic freight</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="36" spans="1:31">
+      <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
       </c>
       <c r="D36">
         <v>53.9</v>
@@ -4133,10 +4255,8 @@
       <c r="T36">
         <v>1.524890063263474</v>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U36" t="s">
+        <v>34</v>
       </c>
       <c r="V36">
         <v>187</v>
@@ -4165,27 +4285,19 @@
       <c r="AD36">
         <v>1588.43</v>
       </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>REDUCIDA</t>
-        </is>
+      <c r="AE36" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>droideka freight lines</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Pandora</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="37" spans="1:31">
+      <c r="A37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>46</v>
       </c>
       <c r="D37">
         <v>54.39</v>
@@ -4238,10 +4350,8 @@
       <c r="T37">
         <v>2.191719726984299</v>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U37" t="s">
+        <v>34</v>
       </c>
       <c r="V37">
         <v>298</v>
@@ -4270,27 +4380,19 @@
       <c r="AD37">
         <v>1642.82</v>
       </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE37" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>coruscant cargo</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Coruscant</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="38" spans="1:31">
+      <c r="A38" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
       </c>
       <c r="D38">
         <v>54.4</v>
@@ -4343,10 +4445,8 @@
       <c r="T38">
         <v>1.163082096834156</v>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U38" t="s">
+        <v>34</v>
       </c>
       <c r="V38">
         <v>249</v>
@@ -4375,27 +4475,19 @@
       <c r="AD38">
         <v>1697.22</v>
       </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE38" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>tusken freight lines</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Caprica</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="39" spans="1:31">
+      <c r="A39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
+        <v>38</v>
       </c>
       <c r="D39">
         <v>55.18</v>
@@ -4448,10 +4540,8 @@
       <c r="T39">
         <v>2.135221848648537</v>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U39" t="s">
+        <v>34</v>
       </c>
       <c r="V39">
         <v>99</v>
@@ -4480,27 +4570,19 @@
       <c r="AD39">
         <v>1752.4</v>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE39" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>betazoid transport</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="40" spans="1:31">
+      <c r="A40" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C40" t="s">
+        <v>46</v>
       </c>
       <c r="D40">
         <v>56.25</v>
@@ -4553,10 +4635,8 @@
       <c r="T40">
         <v>1.618740907016521</v>
       </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U40" t="s">
+        <v>34</v>
       </c>
       <c r="V40">
         <v>395</v>
@@ -4585,27 +4665,19 @@
       <c r="AD40">
         <v>1808.65</v>
       </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE40" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>jedha star movers</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Coruscant</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="41" spans="1:31">
+      <c r="A41" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
       </c>
       <c r="D41">
         <v>57.01</v>
@@ -4658,10 +4730,8 @@
       <c r="T41">
         <v>1.973532887893086</v>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U41" t="s">
+        <v>34</v>
       </c>
       <c r="V41">
         <v>189</v>
@@ -4690,27 +4760,19 @@
       <c r="AD41">
         <v>1865.66</v>
       </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE41" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>photon pack freight</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Naboo</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="42" spans="1:31">
+      <c r="A42" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" t="s">
+        <v>49</v>
       </c>
       <c r="D42">
         <v>57.78</v>
@@ -4760,10 +4822,8 @@
       <c r="T42">
         <v>1.170614079776853</v>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U42" t="s">
+        <v>34</v>
       </c>
       <c r="V42">
         <v>274</v>
@@ -4792,27 +4852,19 @@
       <c r="AD42">
         <v>1923.44</v>
       </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE42" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>sy snootles haulage</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="43" spans="1:31">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" t="s">
+        <v>46</v>
       </c>
       <c r="D43">
         <v>58.86</v>
@@ -4865,10 +4917,8 @@
       <c r="T43">
         <v>2.050918176217969</v>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U43" t="s">
+        <v>34</v>
       </c>
       <c r="V43">
         <v>251</v>
@@ -4897,27 +4947,19 @@
       <c r="AD43">
         <v>1982.3</v>
       </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE43" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>tatooine movers</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Tatooine</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="44" spans="1:31">
+      <c r="A44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
       </c>
       <c r="D44">
         <v>58.94</v>
@@ -4970,10 +5012,8 @@
       <c r="T44">
         <v>2.186549957726859</v>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U44" t="s">
+        <v>34</v>
       </c>
       <c r="V44">
         <v>292</v>
@@ -5002,27 +5042,19 @@
       <c r="AD44">
         <v>2041.24</v>
       </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE44" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>infinity freight co.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Pandora</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="45" spans="1:31">
+      <c r="A45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" t="s">
+        <v>46</v>
       </c>
       <c r="D45">
         <v>59.15</v>
@@ -5075,10 +5107,8 @@
       <c r="T45">
         <v>1.432096189918217</v>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U45" t="s">
+        <v>34</v>
       </c>
       <c r="V45">
         <v>354</v>
@@ -5107,27 +5137,19 @@
       <c r="AD45">
         <v>2100.39</v>
       </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE45" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>andor cargo lines</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Tatooine</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="46" spans="1:31">
+      <c r="A46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>49</v>
       </c>
       <c r="D46">
         <v>59.28</v>
@@ -5180,10 +5202,8 @@
       <c r="T46">
         <v>2.996916807420913</v>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U46" t="s">
+        <v>34</v>
       </c>
       <c r="V46">
         <v>156</v>
@@ -5212,27 +5232,19 @@
       <c r="AD46">
         <v>2159.67</v>
       </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE46" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>bene gesserit goods</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Mann</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="47" spans="1:31">
+      <c r="A47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>33</v>
       </c>
       <c r="D47">
         <v>59.68</v>
@@ -5285,10 +5297,8 @@
       <c r="T47">
         <v>1.865971688285881</v>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U47" t="s">
+        <v>34</v>
       </c>
       <c r="V47">
         <v>155</v>
@@ -5317,27 +5327,19 @@
       <c r="AD47">
         <v>2219.35</v>
       </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE47" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>borg freight lines</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Miller</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="48" spans="1:31">
+      <c r="A48" t="s">
+        <v>110</v>
+      </c>
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s">
+        <v>33</v>
       </c>
       <c r="D48">
         <v>61.09</v>
@@ -5390,10 +5392,8 @@
       <c r="T48">
         <v>1.014311423355463</v>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U48" t="s">
+        <v>34</v>
       </c>
       <c r="V48">
         <v>129</v>
@@ -5422,27 +5422,19 @@
       <c r="AD48">
         <v>2280.44</v>
       </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE48" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>uhura cargo systems</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Endor</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="49" spans="1:31">
+      <c r="A49" t="s">
+        <v>112</v>
+      </c>
+      <c r="B49" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>49</v>
       </c>
       <c r="D49">
         <v>61.47</v>
@@ -5495,10 +5487,8 @@
       <c r="T49">
         <v>2.098841960112588</v>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U49" t="s">
+        <v>34</v>
       </c>
       <c r="V49">
         <v>278</v>
@@ -5527,27 +5517,19 @@
       <c r="AD49">
         <v>2341.91</v>
       </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE49" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>janeway star transport</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Qo'noS</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="50" spans="1:31">
+      <c r="A50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" t="s">
+        <v>114</v>
+      </c>
+      <c r="C50" t="s">
+        <v>38</v>
       </c>
       <c r="D50">
         <v>62.2</v>
@@ -5600,10 +5582,8 @@
       <c r="T50">
         <v>1.349654161777267</v>
       </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U50" t="s">
+        <v>34</v>
       </c>
       <c r="V50">
         <v>251</v>
@@ -5632,27 +5612,19 @@
       <c r="AD50">
         <v>2404.11</v>
       </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE50" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>geonosis freight</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Fhloston Paradise</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="51" spans="1:31">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
       </c>
       <c r="D51">
         <v>65.56999999999999</v>
@@ -5705,10 +5677,8 @@
       <c r="T51">
         <v>1.602626058204834</v>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U51" t="s">
+        <v>34</v>
       </c>
       <c r="V51">
         <v>68</v>
@@ -5737,27 +5707,19 @@
       <c r="AD51">
         <v>2469.68</v>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE51" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>kobol cargo systems</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="52" spans="1:31">
+      <c r="A52" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" t="s">
+        <v>33</v>
       </c>
       <c r="D52">
         <v>67.45999999999999</v>
@@ -5810,10 +5772,8 @@
       <c r="T52">
         <v>0.7614165389296269</v>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>ANTIGUA</t>
-        </is>
+      <c r="U52" t="s">
+        <v>34</v>
       </c>
       <c r="V52">
         <v>42</v>
@@ -5842,27 +5802,19 @@
       <c r="AD52">
         <v>2537.14</v>
       </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE52" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>eros star freight</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Tatooine</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="53" spans="1:31">
+      <c r="A53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" t="s">
+        <v>49</v>
       </c>
       <c r="D53">
         <v>159.08</v>
@@ -5915,10 +5867,8 @@
       <c r="T53">
         <v>5.460557260927386</v>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U53" t="s">
+        <v>118</v>
       </c>
       <c r="V53">
         <v>373</v>
@@ -5947,27 +5897,19 @@
       <c r="AD53">
         <v>2696.22</v>
       </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE53" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>enterprise logistics</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Naboo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="54" spans="1:31">
+      <c r="A54" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" t="s">
+        <v>49</v>
       </c>
       <c r="D54">
         <v>164.25</v>
@@ -6020,10 +5962,8 @@
       <c r="T54">
         <v>5.168430645276198</v>
       </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U54" t="s">
+        <v>118</v>
       </c>
       <c r="V54">
         <v>470</v>
@@ -6052,27 +5992,19 @@
       <c r="AD54">
         <v>2860.47</v>
       </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE54" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>echo base transport</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Qo'noS</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="55" spans="1:31">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" t="s">
+        <v>38</v>
       </c>
       <c r="D55">
         <v>174.29</v>
@@ -6125,10 +6057,8 @@
       <c r="T55">
         <v>9.752922074072115</v>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U55" t="s">
+        <v>118</v>
       </c>
       <c r="V55">
         <v>534</v>
@@ -6157,27 +6087,19 @@
       <c r="AD55">
         <v>3034.76</v>
       </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE55" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>adama transport</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Mül</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="56" spans="1:31">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" t="s">
+        <v>62</v>
       </c>
       <c r="D56">
         <v>174.91</v>
@@ -6230,10 +6152,8 @@
       <c r="T56">
         <v>9.00904123872782</v>
       </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U56" t="s">
+        <v>118</v>
       </c>
       <c r="V56">
         <v>592</v>
@@ -6262,27 +6182,19 @@
       <c r="AD56">
         <v>3209.67</v>
       </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE56" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>raddus logistics</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Dagobah</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="57" spans="1:31">
+      <c r="A57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
       </c>
       <c r="D57">
         <v>180.78</v>
@@ -6335,10 +6247,8 @@
       <c r="T57">
         <v>8.474958729585905</v>
       </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U57" t="s">
+        <v>118</v>
       </c>
       <c r="V57">
         <v>174</v>
@@ -6367,27 +6277,19 @@
       <c r="AD57">
         <v>3390.45</v>
       </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE57" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>mustafar haulage</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Mustafar</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="58" spans="1:31">
+      <c r="A58" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" t="s">
+        <v>49</v>
       </c>
       <c r="D58">
         <v>183.05</v>
@@ -6440,10 +6342,8 @@
       <c r="T58">
         <v>12.02941996668938</v>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U58" t="s">
+        <v>118</v>
       </c>
       <c r="V58">
         <v>552</v>
@@ -6472,27 +6372,19 @@
       <c r="AD58">
         <v>3573.5</v>
       </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE58" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>atlas star transport</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Klendathu</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="59" spans="1:31">
+      <c r="A59" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
       </c>
       <c r="D59">
         <v>184.86</v>
@@ -6545,10 +6437,8 @@
       <c r="T59">
         <v>4.984653955856547</v>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U59" t="s">
+        <v>118</v>
       </c>
       <c r="V59">
         <v>272</v>
@@ -6577,27 +6467,19 @@
       <c r="AD59">
         <v>3758.36</v>
       </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE59" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>hoth haulage</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Hoth</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="60" spans="1:31">
+      <c r="A60" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" t="s">
+        <v>49</v>
       </c>
       <c r="D60">
         <v>185.19</v>
@@ -6650,10 +6532,8 @@
       <c r="T60">
         <v>11.25530544204956</v>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U60" t="s">
+        <v>118</v>
       </c>
       <c r="V60">
         <v>1335</v>
@@ -6682,27 +6562,19 @@
       <c r="AD60">
         <v>3943.55</v>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE60" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>mos eisley haulage</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="61" spans="1:31">
+      <c r="A61" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" t="s">
+        <v>33</v>
       </c>
       <c r="D61">
         <v>186.42</v>
@@ -6755,10 +6627,8 @@
       <c r="T61">
         <v>16.26032319239585</v>
       </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U61" t="s">
+        <v>118</v>
       </c>
       <c r="V61">
         <v>292</v>
@@ -6787,27 +6657,19 @@
       <c r="AD61">
         <v>4129.97</v>
       </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE61" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>tannhäuser freight</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Pandora</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="62" spans="1:31">
+      <c r="A62" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" t="s">
+        <v>77</v>
+      </c>
+      <c r="C62" t="s">
+        <v>46</v>
       </c>
       <c r="D62">
         <v>190.52</v>
@@ -6860,10 +6722,8 @@
       <c r="T62">
         <v>5.993190513488735</v>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U62" t="s">
+        <v>118</v>
       </c>
       <c r="V62">
         <v>2045</v>
@@ -6892,27 +6752,19 @@
       <c r="AD62">
         <v>4320.49</v>
       </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE62" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>unn freightways</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="63" spans="1:31">
+      <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" t="s">
+        <v>46</v>
       </c>
       <c r="D63">
         <v>193.48</v>
@@ -6965,10 +6817,8 @@
       <c r="T63">
         <v>12.1528991878044</v>
       </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U63" t="s">
+        <v>118</v>
       </c>
       <c r="V63">
         <v>170</v>
@@ -6997,27 +6847,19 @@
       <c r="AD63">
         <v>4513.97</v>
       </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE63" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>veritech haulage</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Fhloston Paradise</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="64" spans="1:31">
+      <c r="A64" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" t="s">
+        <v>85</v>
+      </c>
+      <c r="C64" t="s">
+        <v>62</v>
       </c>
       <c r="D64">
         <v>197.46</v>
@@ -7070,10 +6912,8 @@
       <c r="T64">
         <v>13.43005613795645</v>
       </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U64" t="s">
+        <v>118</v>
       </c>
       <c r="V64">
         <v>391</v>
@@ -7102,27 +6942,19 @@
       <c r="AD64">
         <v>4711.43</v>
       </c>
-      <c r="AE64" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE64" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>bib fortuna haulage</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Miranda</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="65" spans="1:31">
+      <c r="A65" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>62</v>
       </c>
       <c r="D65">
         <v>199.68</v>
@@ -7175,10 +7007,8 @@
       <c r="T65">
         <v>11.90777689208659</v>
       </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U65" t="s">
+        <v>118</v>
       </c>
       <c r="V65">
         <v>215</v>
@@ -7207,27 +7037,19 @@
       <c r="AD65">
         <v>4911.11</v>
       </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE65" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>event horizon haulage</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Planet P</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="66" spans="1:31">
+      <c r="A66" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" t="s">
+        <v>46</v>
       </c>
       <c r="D66">
         <v>204.46</v>
@@ -7280,10 +7102,8 @@
       <c r="T66">
         <v>14.31766337306996</v>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U66" t="s">
+        <v>118</v>
       </c>
       <c r="V66">
         <v>198</v>
@@ -7312,27 +7132,19 @@
       <c r="AD66">
         <v>5115.57</v>
       </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE66" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>naboo star movers</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Naboo</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="67" spans="1:31">
+      <c r="A67" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" t="s">
+        <v>49</v>
       </c>
       <c r="D67">
         <v>209.15</v>
@@ -7385,10 +7197,8 @@
       <c r="T67">
         <v>11.91863679734531</v>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U67" t="s">
+        <v>118</v>
       </c>
       <c r="V67">
         <v>476</v>
@@ -7417,27 +7227,19 @@
       <c r="AD67">
         <v>5324.72</v>
       </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE67" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>batty haulage</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Zegema Beach</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="68" spans="1:31">
+      <c r="A68" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" t="s">
+        <v>33</v>
       </c>
       <c r="D68">
         <v>209.19</v>
@@ -7490,10 +7292,8 @@
       <c r="T68">
         <v>7.842235161640193</v>
       </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U68" t="s">
+        <v>118</v>
       </c>
       <c r="V68">
         <v>542</v>
@@ -7522,27 +7322,19 @@
       <c r="AD68">
         <v>5533.91</v>
       </c>
-      <c r="AE68" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE68" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>hyperion star haulage</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="69" spans="1:31">
+      <c r="A69" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69" t="s">
+        <v>46</v>
       </c>
       <c r="D69">
         <v>211.14</v>
@@ -7595,10 +7387,8 @@
       <c r="T69">
         <v>18.42200014570097</v>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U69" t="s">
+        <v>118</v>
       </c>
       <c r="V69">
         <v>244</v>
@@ -7627,27 +7417,19 @@
       <c r="AD69">
         <v>5745.05</v>
       </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
+      <c r="AE69" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>rogue one freight</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="70" spans="1:31">
+      <c r="A70" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" t="s">
+        <v>33</v>
       </c>
       <c r="D70">
         <v>216.11</v>
@@ -7700,10 +7482,8 @@
       <c r="T70">
         <v>8.506372716892811</v>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U70" t="s">
+        <v>118</v>
       </c>
       <c r="V70">
         <v>299</v>
@@ -7732,27 +7512,19 @@
       <c r="AD70">
         <v>5961.16</v>
       </c>
-      <c r="AE70" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE70" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>mirror universe cargo</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="71" spans="1:31">
+      <c r="A71" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" t="s">
+        <v>33</v>
       </c>
       <c r="D71">
         <v>217.7</v>
@@ -7805,10 +7577,8 @@
       <c r="T71">
         <v>12.30771456228866</v>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U71" t="s">
+        <v>118</v>
       </c>
       <c r="V71">
         <v>613</v>
@@ -7837,27 +7607,19 @@
       <c r="AD71">
         <v>6178.86</v>
       </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE71" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>bajoran star transport</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Mustafar</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="72" spans="1:31">
+      <c r="A72" t="s">
+        <v>138</v>
+      </c>
+      <c r="B72" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" t="s">
+        <v>49</v>
       </c>
       <c r="D72">
         <v>219.85</v>
@@ -7910,10 +7672,8 @@
       <c r="T72">
         <v>7.685939469952849</v>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U72" t="s">
+        <v>118</v>
       </c>
       <c r="V72">
         <v>92</v>
@@ -7942,27 +7702,19 @@
       <c r="AD72">
         <v>6398.71</v>
       </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE72" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>jovian logistics</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Miranda</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="73" spans="1:31">
+      <c r="A73" t="s">
+        <v>139</v>
+      </c>
+      <c r="B73" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" t="s">
+        <v>62</v>
       </c>
       <c r="D73">
         <v>220.56</v>
@@ -8015,10 +7767,8 @@
       <c r="T73">
         <v>61.91487701865828</v>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U73" t="s">
+        <v>118</v>
       </c>
       <c r="V73">
         <v>406</v>
@@ -8047,27 +7797,19 @@
       <c r="AD73">
         <v>6619.27</v>
       </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE73" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>star gate logistics</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Miller</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="74" spans="1:31">
+      <c r="A74" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" t="s">
+        <v>111</v>
+      </c>
+      <c r="C74" t="s">
+        <v>33</v>
       </c>
       <c r="D74">
         <v>220.65</v>
@@ -8120,10 +7862,8 @@
       <c r="T74">
         <v>4.910074888477629</v>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U74" t="s">
+        <v>118</v>
       </c>
       <c r="V74">
         <v>570</v>
@@ -8152,27 +7892,19 @@
       <c r="AD74">
         <v>6839.92</v>
       </c>
-      <c r="AE74" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE74" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>forest moon freight</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Mül</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="75" spans="1:31">
+      <c r="A75" t="s">
+        <v>141</v>
+      </c>
+      <c r="B75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" t="s">
+        <v>62</v>
       </c>
       <c r="D75">
         <v>222.49</v>
@@ -8225,10 +7957,8 @@
       <c r="T75">
         <v>8.858008824422832</v>
       </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U75" t="s">
+        <v>118</v>
       </c>
       <c r="V75">
         <v>535</v>
@@ -8257,27 +7987,19 @@
       <c r="AD75">
         <v>7062.41</v>
       </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE75" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>solaris haulage</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Naboo</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="76" spans="1:31">
+      <c r="A76" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" t="s">
+        <v>49</v>
       </c>
       <c r="D76">
         <v>225.99</v>
@@ -8330,10 +8052,8 @@
       <c r="T76">
         <v>8.14439354343134</v>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U76" t="s">
+        <v>118</v>
       </c>
       <c r="V76">
         <v>229</v>
@@ -8362,27 +8082,19 @@
       <c r="AD76">
         <v>7288.4</v>
       </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE76" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>vulcan star freight</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Kobol</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="77" spans="1:31">
+      <c r="A77" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" t="s">
+        <v>33</v>
       </c>
       <c r="D77">
         <v>226.22</v>
@@ -8435,10 +8147,8 @@
       <c r="T77">
         <v>19.16974675120676</v>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U77" t="s">
+        <v>118</v>
       </c>
       <c r="V77">
         <v>240</v>
@@ -8467,27 +8177,19 @@
       <c r="AD77">
         <v>7514.62</v>
       </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE77" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>defiant cargo</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Tatooine</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="78" spans="1:31">
+      <c r="A78" t="s">
+        <v>144</v>
+      </c>
+      <c r="B78" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" t="s">
+        <v>49</v>
       </c>
       <c r="D78">
         <v>230.75</v>
@@ -8540,10 +8242,8 @@
       <c r="T78">
         <v>12.42489418871954</v>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U78" t="s">
+        <v>118</v>
       </c>
       <c r="V78">
         <v>438</v>
@@ -8572,27 +8272,19 @@
       <c r="AD78">
         <v>7745.37</v>
       </c>
-      <c r="AE78" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE78" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>rebel alliance transport</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Miller</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Pequeña Nube de Magallanes</t>
-        </is>
+    <row r="79" spans="1:31">
+      <c r="A79" t="s">
+        <v>145</v>
+      </c>
+      <c r="B79" t="s">
+        <v>111</v>
+      </c>
+      <c r="C79" t="s">
+        <v>33</v>
       </c>
       <c r="D79">
         <v>232.97</v>
@@ -8645,10 +8337,8 @@
       <c r="T79">
         <v>22.81150119148251</v>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U79" t="s">
+        <v>118</v>
       </c>
       <c r="V79">
         <v>521</v>
@@ -8677,27 +8367,19 @@
       <c r="AD79">
         <v>7978.34</v>
       </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE79" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>kashyyyk freight lines</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Fhloston Paradise</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="80" spans="1:31">
+      <c r="A80" t="s">
+        <v>146</v>
+      </c>
+      <c r="B80" t="s">
+        <v>85</v>
+      </c>
+      <c r="C80" t="s">
+        <v>62</v>
       </c>
       <c r="D80">
         <v>238.14</v>
@@ -8747,10 +8429,8 @@
       <c r="T80">
         <v>7.651065790224991</v>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U80" t="s">
+        <v>118</v>
       </c>
       <c r="V80">
         <v>329</v>
@@ -8773,27 +8453,19 @@
       <c r="AD80">
         <v>8216.48</v>
       </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE80" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>shuttlepod movers</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Arrakis</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="81" spans="1:31">
+      <c r="A81" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81" t="s">
+        <v>62</v>
       </c>
       <c r="D81">
         <v>249.39</v>
@@ -8846,10 +8518,8 @@
       <c r="T81">
         <v>18.50505207366464</v>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U81" t="s">
+        <v>118</v>
       </c>
       <c r="V81">
         <v>594</v>
@@ -8878,27 +8548,19 @@
       <c r="AD81">
         <v>8465.870000000001</v>
       </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE81" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>harkonnen heavy haul</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Naboo</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="82" spans="1:31">
+      <c r="A82" t="s">
+        <v>148</v>
+      </c>
+      <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" t="s">
+        <v>49</v>
       </c>
       <c r="D82">
         <v>461.56</v>
@@ -8951,10 +8613,8 @@
       <c r="T82">
         <v>41.13842896380448</v>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U82" t="s">
+        <v>149</v>
       </c>
       <c r="V82">
         <v>350</v>
@@ -8983,27 +8643,19 @@
       <c r="AD82">
         <v>8927.43</v>
       </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE82" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>travis star haulage</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>La Tierra (Final)</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="83" spans="1:31">
+      <c r="A83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B83" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" t="s">
+        <v>38</v>
       </c>
       <c r="D83">
         <v>466.63</v>
@@ -9056,10 +8708,8 @@
       <c r="T83">
         <v>63.93700808672348</v>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U83" t="s">
+        <v>149</v>
       </c>
       <c r="V83">
         <v>415</v>
@@ -9088,27 +8738,19 @@
       <c r="AD83">
         <v>9394.059999999999</v>
       </c>
-      <c r="AE83" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE83" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>seven of nine logistics</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Arrakis</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="84" spans="1:31">
+      <c r="A84" t="s">
+        <v>151</v>
+      </c>
+      <c r="B84" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84" t="s">
+        <v>62</v>
       </c>
       <c r="D84">
         <v>477.8</v>
@@ -9161,10 +8803,8 @@
       <c r="T84">
         <v>34.81478871121933</v>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U84" t="s">
+        <v>149</v>
       </c>
       <c r="V84">
         <v>317</v>
@@ -9193,27 +8833,19 @@
       <c r="AD84">
         <v>9871.860000000001</v>
       </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE84" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>assimilator haulage</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Coruscant</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="85" spans="1:31">
+      <c r="A85" t="s">
+        <v>152</v>
+      </c>
+      <c r="B85" t="s">
+        <v>98</v>
+      </c>
+      <c r="C85" t="s">
+        <v>49</v>
       </c>
       <c r="D85">
         <v>482.75</v>
@@ -9266,10 +8898,8 @@
       <c r="T85">
         <v>28.03511729454446</v>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U85" t="s">
+        <v>149</v>
       </c>
       <c r="V85">
         <v>466</v>
@@ -9298,27 +8928,19 @@
       <c r="AD85">
         <v>10354.61</v>
       </c>
-      <c r="AE85" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE85" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>yoda logistics</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Arrakis</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="86" spans="1:31">
+      <c r="A86" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" t="s">
+        <v>92</v>
+      </c>
+      <c r="C86" t="s">
+        <v>62</v>
       </c>
       <c r="D86">
         <v>488.65</v>
@@ -9371,10 +8993,8 @@
       <c r="T86">
         <v>32.84601069622666</v>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U86" t="s">
+        <v>149</v>
       </c>
       <c r="V86">
         <v>330</v>
@@ -9403,27 +9023,19 @@
       <c r="AD86">
         <v>10843.26</v>
       </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE86" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>super star logistics</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Arrakis</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="87" spans="1:31">
+      <c r="A87" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" t="s">
+        <v>62</v>
       </c>
       <c r="D87">
         <v>490.17</v>
@@ -9476,10 +9088,8 @@
       <c r="T87">
         <v>45.79397109651696</v>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U87" t="s">
+        <v>149</v>
       </c>
       <c r="V87">
         <v>406</v>
@@ -9508,27 +9118,19 @@
       <c r="AD87">
         <v>11333.43</v>
       </c>
-      <c r="AE87" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE87" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>andromeda cargo</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Tatooine</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="88" spans="1:31">
+      <c r="A88" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" t="s">
+        <v>106</v>
+      </c>
+      <c r="C88" t="s">
+        <v>49</v>
       </c>
       <c r="D88">
         <v>493.83</v>
@@ -9581,10 +9183,8 @@
       <c r="T88">
         <v>64.09759398355686</v>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U88" t="s">
+        <v>149</v>
       </c>
       <c r="V88">
         <v>804</v>
@@ -9613,27 +9213,19 @@
       <c r="AD88">
         <v>11827.26</v>
       </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE88" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>io star transport</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Miranda</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="89" spans="1:31">
+      <c r="A89" t="s">
+        <v>156</v>
+      </c>
+      <c r="B89" t="s">
+        <v>69</v>
+      </c>
+      <c r="C89" t="s">
+        <v>62</v>
       </c>
       <c r="D89">
         <v>498</v>
@@ -9686,10 +9278,8 @@
       <c r="T89">
         <v>63.78935012090904</v>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U89" t="s">
+        <v>118</v>
       </c>
       <c r="V89">
         <v>646</v>
@@ -9718,27 +9308,19 @@
       <c r="AD89">
         <v>12325.26</v>
       </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE89" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>battle droid haulage</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Fhloston Paradise</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="90" spans="1:31">
+      <c r="A90" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" t="s">
+        <v>85</v>
+      </c>
+      <c r="C90" t="s">
+        <v>62</v>
       </c>
       <c r="D90">
         <v>501.07</v>
@@ -9791,10 +9373,8 @@
       <c r="T90">
         <v>39.74810409634606</v>
       </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U90" t="s">
+        <v>149</v>
       </c>
       <c r="V90">
         <v>292</v>
@@ -9823,27 +9403,19 @@
       <c r="AD90">
         <v>12826.33</v>
       </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE90" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>kamino movers</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>LV-223</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="91" spans="1:31">
+      <c r="A91" t="s">
+        <v>158</v>
+      </c>
+      <c r="B91" t="s">
+        <v>159</v>
+      </c>
+      <c r="C91" t="s">
+        <v>46</v>
       </c>
       <c r="D91">
         <v>505.96</v>
@@ -9896,10 +9468,8 @@
       <c r="T91">
         <v>53.57015140034163</v>
       </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U91" t="s">
+        <v>149</v>
       </c>
       <c r="V91">
         <v>536</v>
@@ -9928,27 +9498,19 @@
       <c r="AD91">
         <v>13332.29</v>
       </c>
-      <c r="AE91" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE91" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>dagobah freightlines</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Dagobah</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="92" spans="1:31">
+      <c r="A92" t="s">
+        <v>160</v>
+      </c>
+      <c r="B92" t="s">
+        <v>55</v>
+      </c>
+      <c r="C92" t="s">
+        <v>49</v>
       </c>
       <c r="D92">
         <v>511.39</v>
@@ -10001,10 +9563,8 @@
       <c r="T92">
         <v>36.10474274271244</v>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U92" t="s">
+        <v>149</v>
       </c>
       <c r="V92">
         <v>389</v>
@@ -10033,27 +9593,19 @@
       <c r="AD92">
         <v>13843.68</v>
       </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE92" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>hal intergalactic freight</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Klendathu</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="93" spans="1:31">
+      <c r="A93" t="s">
+        <v>161</v>
+      </c>
+      <c r="B93" t="s">
+        <v>90</v>
+      </c>
+      <c r="C93" t="s">
+        <v>46</v>
       </c>
       <c r="D93">
         <v>515.75</v>
@@ -10106,10 +9658,8 @@
       <c r="T93">
         <v>72.66621363268264</v>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U93" t="s">
+        <v>149</v>
       </c>
       <c r="V93">
         <v>283</v>
@@ -10138,27 +9688,19 @@
       <c r="AD93">
         <v>14359.43</v>
       </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE93" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>dune dynamics</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Mül</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="94" spans="1:31">
+      <c r="A94" t="s">
+        <v>162</v>
+      </c>
+      <c r="B94" t="s">
+        <v>61</v>
+      </c>
+      <c r="C94" t="s">
+        <v>62</v>
       </c>
       <c r="D94">
         <v>515.86</v>
@@ -10211,10 +9753,8 @@
       <c r="T94">
         <v>48.50096462333022</v>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U94" t="s">
+        <v>149</v>
       </c>
       <c r="V94">
         <v>370</v>
@@ -10243,27 +9783,19 @@
       <c r="AD94">
         <v>14875.29</v>
       </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE94" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>sith transport corp.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Tatooine</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="95" spans="1:31">
+      <c r="A95" t="s">
+        <v>163</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95" t="s">
+        <v>49</v>
       </c>
       <c r="D95">
         <v>515.98</v>
@@ -10316,10 +9848,8 @@
       <c r="T95">
         <v>27.7505969424173</v>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U95" t="s">
+        <v>149</v>
       </c>
       <c r="V95">
         <v>618</v>
@@ -10348,27 +9878,19 @@
       <c r="AD95">
         <v>15391.27</v>
       </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE95" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>kyber crystal shipping</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Coruscant</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="96" spans="1:31">
+      <c r="A96" t="s">
+        <v>164</v>
+      </c>
+      <c r="B96" t="s">
+        <v>98</v>
+      </c>
+      <c r="C96" t="s">
+        <v>49</v>
       </c>
       <c r="D96">
         <v>517.61</v>
@@ -10421,10 +9943,8 @@
       <c r="T96">
         <v>60.19998605635057</v>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U96" t="s">
+        <v>149</v>
       </c>
       <c r="V96">
         <v>275</v>
@@ -10453,27 +9973,19 @@
       <c r="AD96">
         <v>15908.88</v>
       </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE96" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>zion cargo systems</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="97" spans="1:31">
+      <c r="A97" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97" t="s">
+        <v>94</v>
+      </c>
+      <c r="C97" t="s">
+        <v>46</v>
       </c>
       <c r="D97">
         <v>519.87</v>
@@ -10526,10 +10038,8 @@
       <c r="T97">
         <v>32.05525831522932</v>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U97" t="s">
+        <v>149</v>
       </c>
       <c r="V97">
         <v>369</v>
@@ -10558,27 +10068,19 @@
       <c r="AD97">
         <v>16428.75</v>
       </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE97" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>moya cargo systems</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Nueva Caprica</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="98" spans="1:31">
+      <c r="A98" t="s">
+        <v>166</v>
+      </c>
+      <c r="B98" t="s">
+        <v>167</v>
+      </c>
+      <c r="C98" t="s">
+        <v>38</v>
       </c>
       <c r="D98">
         <v>520.29</v>
@@ -10631,10 +10133,8 @@
       <c r="T98">
         <v>36.05966884068395</v>
       </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U98" t="s">
+        <v>149</v>
       </c>
       <c r="V98">
         <v>400</v>
@@ -10663,27 +10163,19 @@
       <c r="AD98">
         <v>16949.04</v>
       </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE98" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>icarus star transport</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Tierra</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Vía Láctea</t>
-        </is>
+    <row r="99" spans="1:31">
+      <c r="A99" t="s">
+        <v>168</v>
+      </c>
+      <c r="B99" t="s">
+        <v>94</v>
+      </c>
+      <c r="C99" t="s">
+        <v>46</v>
       </c>
       <c r="D99">
         <v>523.86</v>
@@ -10736,10 +10228,8 @@
       <c r="T99">
         <v>31.50017540382977</v>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U99" t="s">
+        <v>149</v>
       </c>
       <c r="V99">
         <v>656</v>
@@ -10768,27 +10258,19 @@
       <c r="AD99">
         <v>17472.9</v>
       </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE99" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ezra bridger haulage</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Fhloston Paradise</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="100" spans="1:31">
+      <c r="A100" t="s">
+        <v>169</v>
+      </c>
+      <c r="B100" t="s">
+        <v>85</v>
+      </c>
+      <c r="C100" t="s">
+        <v>62</v>
       </c>
       <c r="D100">
         <v>534.88</v>
@@ -10841,10 +10323,8 @@
       <c r="T100">
         <v>62.79876701612827</v>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U100" t="s">
+        <v>149</v>
       </c>
       <c r="V100">
         <v>335</v>
@@ -10870,27 +10350,19 @@
       <c r="AD100">
         <v>18007.78</v>
       </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE100" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>home one cargo</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Coruscant</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Galaxia de Andrómeda</t>
-        </is>
+    <row r="101" spans="1:31">
+      <c r="A101" t="s">
+        <v>170</v>
+      </c>
+      <c r="B101" t="s">
+        <v>98</v>
+      </c>
+      <c r="C101" t="s">
+        <v>49</v>
       </c>
       <c r="D101">
         <v>1145.48</v>
@@ -10943,10 +10415,8 @@
       <c r="T101">
         <v>202.4779489786356</v>
       </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U101" t="s">
+        <v>149</v>
       </c>
       <c r="V101">
         <v>651</v>
@@ -10975,27 +10445,19 @@
       <c r="AD101">
         <v>19153.26</v>
       </c>
-      <c r="AE101" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE101" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>chakotay cargo systems</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Romulus</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="102" spans="1:31">
+      <c r="A102" t="s">
+        <v>171</v>
+      </c>
+      <c r="B102" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" t="s">
+        <v>38</v>
       </c>
       <c r="D102">
         <v>2158.69</v>
@@ -11048,10 +10510,8 @@
       <c r="T102">
         <v>56.06391922960216</v>
       </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U102" t="s">
+        <v>149</v>
       </c>
       <c r="V102">
         <v>1229</v>
@@ -11080,27 +10540,19 @@
       <c r="AD102">
         <v>21311.95</v>
       </c>
-      <c r="AE102" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE102" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>hyperdrive express</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Miranda</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="103" spans="1:31">
+      <c r="A103" t="s">
+        <v>172</v>
+      </c>
+      <c r="B103" t="s">
+        <v>69</v>
+      </c>
+      <c r="C103" t="s">
+        <v>62</v>
       </c>
       <c r="D103">
         <v>2499.94</v>
@@ -11153,10 +10605,8 @@
       <c r="T103">
         <v>47.10892038974923</v>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U103" t="s">
+        <v>149</v>
       </c>
       <c r="V103">
         <v>1028</v>
@@ -11185,27 +10635,19 @@
       <c r="AD103">
         <v>23811.89</v>
       </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE103" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>arrakis freight</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Arrakis</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Gran Nube de Magallanes</t>
-        </is>
+    <row r="104" spans="1:31">
+      <c r="A104" t="s">
+        <v>173</v>
+      </c>
+      <c r="B104" t="s">
+        <v>92</v>
+      </c>
+      <c r="C104" t="s">
+        <v>62</v>
       </c>
       <c r="D104">
         <v>2966.52</v>
@@ -11258,10 +10700,8 @@
       <c r="T104">
         <v>48.82633693970444</v>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>RENOVADA</t>
-        </is>
+      <c r="U104" t="s">
+        <v>149</v>
       </c>
       <c r="V104">
         <v>1165</v>
@@ -11290,27 +10730,19 @@
       <c r="AD104">
         <v>26778.41</v>
       </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
+      <c r="AE104" t="s">
+        <v>136</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>vega transport</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Qo'noS</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Galaxia del Triángulo</t>
-        </is>
+    <row r="105" spans="1:31">
+      <c r="A105" t="s">
+        <v>174</v>
+      </c>
+      <c r="B105" t="s">
+        <v>114</v>
+      </c>
+      <c r="C105" t="s">
+        <v>38</v>
       </c>
       <c r="E105">
         <v>90.89</v>
@@ -11360,10 +10792,8 @@
       <c r="T105">
         <v>21.41235325955999</v>
       </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>MADURA</t>
-        </is>
+      <c r="U105" t="s">
+        <v>118</v>
       </c>
       <c r="V105">
         <v>205</v>
